--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_los_lagos.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_los_lagos.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>28.55637744463224</v>
+      </c>
+      <c r="C2">
         <v>22.86156412563928</v>
-      </c>
-      <c r="C2">
-        <v>28.55637744463224</v>
       </c>
       <c r="D2">
         <v>4.374153905237387</v>
       </c>
       <c r="E2">
-        <v>15.0983191876436</v>
+        <v>18.85930897520457</v>
       </c>
       <c r="F2">
         <v>66.04237183715182</v>
       </c>
       <c r="G2">
-        <v>18.85930897520457</v>
+        <v>15.0983191876436</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>28.32897069999155</v>
+      </c>
+      <c r="C3">
         <v>32.6901967406907</v>
-      </c>
-      <c r="C3">
-        <v>28.32897069999155</v>
       </c>
       <c r="D3">
         <v>3.059021051272117</v>
       </c>
       <c r="E3">
-        <v>20.30205301659718</v>
+        <v>17.59353942158945</v>
       </c>
       <c r="F3">
         <v>62.10440756181337</v>
       </c>
       <c r="G3">
-        <v>17.59353942158945</v>
+        <v>20.30205301659718</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>25.78397212543554</v>
+      </c>
+      <c r="C4">
         <v>44.21215640727836</v>
-      </c>
-      <c r="C4">
-        <v>25.78397212543554</v>
       </c>
       <c r="D4">
         <v>2.261821366024519</v>
       </c>
       <c r="E4">
-        <v>26.00774311090867</v>
+        <v>15.1673878387611</v>
       </c>
       <c r="F4">
         <v>58.82486905033022</v>
       </c>
       <c r="G4">
-        <v>15.1673878387611</v>
+        <v>26.00774311090867</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>27.17528373266078</v>
+      </c>
+      <c r="C5">
         <v>40.61790668348046</v>
-      </c>
-      <c r="C5">
-        <v>27.17528373266078</v>
       </c>
       <c r="D5">
         <v>2.461968332815896</v>
       </c>
       <c r="E5">
-        <v>24.20712460544116</v>
+        <v>16.19570118743424</v>
       </c>
       <c r="F5">
         <v>59.59717420712461</v>
       </c>
       <c r="G5">
-        <v>16.19570118743424</v>
+        <v>24.20712460544116</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>31.94934158451465</v>
+      </c>
+      <c r="C6">
         <v>30.6900769950349</v>
-      </c>
-      <c r="C6">
-        <v>31.94934158451465</v>
       </c>
       <c r="D6">
         <v>3.258382180539273</v>
       </c>
       <c r="E6">
-        <v>18.87001150340678</v>
+        <v>19.64427926732148</v>
       </c>
       <c r="F6">
         <v>61.48570922927174</v>
       </c>
       <c r="G6">
-        <v>19.64427926732148</v>
+        <v>18.87001150340678</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>28.55371534850766</v>
+      </c>
+      <c r="C7">
         <v>38.72996191657072</v>
-      </c>
-      <c r="C7">
-        <v>28.55371534850766</v>
       </c>
       <c r="D7">
         <v>2.581980333866911</v>
       </c>
       <c r="E7">
-        <v>23.15226598898772</v>
+        <v>17.06903854299026</v>
       </c>
       <c r="F7">
         <v>59.77869546802202</v>
       </c>
       <c r="G7">
-        <v>17.06903854299026</v>
+        <v>23.15226598898772</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>27.24572529501485</v>
+      </c>
+      <c r="C8">
         <v>31.99004575740548</v>
-      </c>
-      <c r="C8">
-        <v>27.24572529501485</v>
       </c>
       <c r="D8">
         <v>3.125972396486826</v>
       </c>
       <c r="E8">
-        <v>20.08973583383747</v>
+        <v>17.11030449687437</v>
       </c>
       <c r="F8">
         <v>62.79995966928816</v>
       </c>
       <c r="G8">
-        <v>17.11030449687437</v>
+        <v>20.08973583383747</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>25.17105535973461</v>
+      </c>
+      <c r="C9">
         <v>42.46319718017831</v>
-      </c>
-      <c r="C9">
-        <v>25.17105535973461</v>
       </c>
       <c r="D9">
         <v>2.35498046875</v>
       </c>
       <c r="E9">
-        <v>25.3308596165739</v>
+        <v>15.01546072974644</v>
       </c>
       <c r="F9">
         <v>59.65367965367965</v>
       </c>
       <c r="G9">
-        <v>15.01546072974644</v>
+        <v>25.3308596165739</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.58851038954137</v>
+      </c>
+      <c r="C10">
         <v>25.15278737312005</v>
-      </c>
-      <c r="C10">
-        <v>28.58851038954137</v>
       </c>
       <c r="D10">
         <v>3.975702514261568</v>
       </c>
       <c r="E10">
-        <v>16.36046250367272</v>
+        <v>18.59520558599354</v>
       </c>
       <c r="F10">
         <v>65.04433191033374</v>
       </c>
       <c r="G10">
-        <v>18.59520558599354</v>
+        <v>16.36046250367272</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>25.09772393335366</v>
+      </c>
+      <c r="C11">
         <v>25.15317013667489</v>
-      </c>
-      <c r="C11">
-        <v>25.09772393335366</v>
       </c>
       <c r="D11">
         <v>3.975642014769095</v>
       </c>
       <c r="E11">
-        <v>16.7407790099083</v>
+        <v>16.7038765983357</v>
       </c>
       <c r="F11">
         <v>66.55534439175601</v>
       </c>
       <c r="G11">
-        <v>16.7038765983357</v>
+        <v>16.7407790099083</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>24.89809555629803</v>
+      </c>
+      <c r="C12">
         <v>33.65519545606415</v>
-      </c>
-      <c r="C12">
-        <v>24.89809555629803</v>
       </c>
       <c r="D12">
         <v>2.971309441080115</v>
       </c>
       <c r="E12">
-        <v>21.22642503424297</v>
+        <v>15.7032978611316</v>
       </c>
       <c r="F12">
-        <v>63.07027710462544</v>
+        <v>63.07027710462543</v>
       </c>
       <c r="G12">
-        <v>15.7032978611316</v>
+        <v>21.22642503424296</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>25.33805245485071</v>
+      </c>
+      <c r="C13">
         <v>28.25120246846356</v>
-      </c>
-      <c r="C13">
-        <v>25.33805245485071</v>
       </c>
       <c r="D13">
         <v>3.539672341792483</v>
       </c>
       <c r="E13">
-        <v>18.39399669108958</v>
+        <v>16.49728196643819</v>
       </c>
       <c r="F13">
         <v>65.10872134247222</v>
       </c>
       <c r="G13">
-        <v>16.49728196643819</v>
+        <v>18.39399669108958</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>26.3855421686747</v>
+      </c>
+      <c r="C14">
         <v>36.30522088353413</v>
-      </c>
-      <c r="C14">
-        <v>26.3855421686747</v>
       </c>
       <c r="D14">
         <v>2.754424778761062</v>
       </c>
       <c r="E14">
-        <v>22.31547765983708</v>
+        <v>16.21821772401876</v>
       </c>
       <c r="F14">
         <v>61.46630461614416</v>
       </c>
       <c r="G14">
-        <v>16.21821772401876</v>
+        <v>22.31547765983708</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>27.76031070834104</v>
+      </c>
+      <c r="C15">
         <v>26.49343443684113</v>
-      </c>
-      <c r="C15">
-        <v>27.76031070834104</v>
       </c>
       <c r="D15">
         <v>3.774520069808028</v>
       </c>
       <c r="E15">
-        <v>17.17522930279959</v>
+        <v>17.9965229902284</v>
       </c>
       <c r="F15">
         <v>64.82824770697201</v>
       </c>
       <c r="G15">
-        <v>17.9965229902284</v>
+        <v>17.17522930279959</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>25.42239685658153</v>
+      </c>
+      <c r="C16">
         <v>39.3713163064833</v>
-      </c>
-      <c r="C16">
-        <v>25.42239685658153</v>
       </c>
       <c r="D16">
         <v>2.539920159680639</v>
       </c>
       <c r="E16">
-        <v>23.89127324749642</v>
+        <v>15.42680019074869</v>
       </c>
       <c r="F16">
         <v>60.68192656175489</v>
       </c>
       <c r="G16">
-        <v>15.42680019074869</v>
+        <v>23.89127324749642</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>26.11960311075355</v>
+      </c>
+      <c r="C17">
         <v>33.89648699383213</v>
-      </c>
-      <c r="C17">
-        <v>26.11960311075355</v>
       </c>
       <c r="D17">
         <v>2.950158227848101</v>
       </c>
       <c r="E17">
-        <v>21.18317412435059</v>
+        <v>16.3231104407575</v>
       </c>
       <c r="F17">
         <v>62.4937154348919</v>
       </c>
       <c r="G17">
-        <v>16.3231104407575</v>
+        <v>21.18317412435059</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>29.00099286085764</v>
+      </c>
+      <c r="C18">
         <v>20.19289868091343</v>
-      </c>
-      <c r="C18">
-        <v>29.00099286085764</v>
       </c>
       <c r="D18">
         <v>4.952236010302037</v>
       </c>
       <c r="E18">
-        <v>13.53466852579541</v>
+        <v>19.43845861325897</v>
       </c>
       <c r="F18">
         <v>67.02687286094562</v>
       </c>
       <c r="G18">
-        <v>19.43845861325897</v>
+        <v>13.53466852579541</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>24.46055889635656</v>
+      </c>
+      <c r="C19">
         <v>37.88468340997524</v>
-      </c>
-      <c r="C19">
-        <v>24.46055889635656</v>
       </c>
       <c r="D19">
         <v>2.639589169000934</v>
       </c>
       <c r="E19">
+        <v>15.06700076261031</v>
+      </c>
+      <c r="F19">
+        <v>61.59712386970259</v>
+      </c>
+      <c r="G19">
         <v>23.33587536768711</v>
-      </c>
-      <c r="F19">
-        <v>61.59712386970258</v>
-      </c>
-      <c r="G19">
-        <v>15.06700076261031</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>23.74264566331372</v>
+      </c>
+      <c r="C20">
         <v>36.97096223192256</v>
-      </c>
-      <c r="C20">
-        <v>23.74264566331372</v>
       </c>
       <c r="D20">
         <v>2.70482546201232</v>
       </c>
       <c r="E20">
-        <v>23.00425129900803</v>
+        <v>14.77326405290506</v>
       </c>
       <c r="F20">
         <v>62.22248464808691</v>
       </c>
       <c r="G20">
-        <v>14.77326405290506</v>
+        <v>23.00425129900803</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>26.56251390136923</v>
+      </c>
+      <c r="C21">
         <v>31.05988487442059</v>
-      </c>
-      <c r="C21">
-        <v>26.56251390136923</v>
       </c>
       <c r="D21">
         <v>3.219586949672023</v>
       </c>
       <c r="E21">
-        <v>19.70524818531772</v>
+        <v>16.85199191718501</v>
       </c>
       <c r="F21">
         <v>63.44275989749727</v>
       </c>
       <c r="G21">
-        <v>16.85199191718501</v>
+        <v>19.70524818531772</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>28.9047536130942</v>
+      </c>
+      <c r="C22">
         <v>36.18317952289744</v>
-      </c>
-      <c r="C22">
-        <v>28.9047536130942</v>
       </c>
       <c r="D22">
         <v>2.76371511068335</v>
       </c>
       <c r="E22">
-        <v>21.91751924902436</v>
+        <v>17.50870161375382</v>
       </c>
       <c r="F22">
         <v>60.57377913722181</v>
       </c>
       <c r="G22">
-        <v>17.50870161375382</v>
+        <v>21.91751924902436</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>28.2099490795143</v>
+      </c>
+      <c r="C23">
         <v>40.96357226792009</v>
-      </c>
-      <c r="C23">
-        <v>28.2099490795143</v>
       </c>
       <c r="D23">
         <v>2.441193344807802</v>
       </c>
       <c r="E23">
-        <v>24.21393841166936</v>
+        <v>16.67515628617736</v>
       </c>
       <c r="F23">
         <v>59.11090530215328</v>
       </c>
       <c r="G23">
-        <v>16.67515628617736</v>
+        <v>24.21393841166936</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>25.17673888255416</v>
+      </c>
+      <c r="C24">
         <v>35.49600912200684</v>
-      </c>
-      <c r="C24">
-        <v>25.17673888255416</v>
       </c>
       <c r="D24">
         <v>2.817218117571474</v>
       </c>
       <c r="E24">
-        <v>22.09211553473848</v>
+        <v>15.66957632531403</v>
       </c>
       <c r="F24">
         <v>62.23830813994748</v>
       </c>
       <c r="G24">
-        <v>15.66957632531403</v>
+        <v>22.09211553473848</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>26.89444161142274</v>
+      </c>
+      <c r="C25">
         <v>39.77562468128506</v>
-      </c>
-      <c r="C25">
-        <v>26.89444161142274</v>
       </c>
       <c r="D25">
         <v>2.514102564102564</v>
       </c>
       <c r="E25">
-        <v>23.86488801860238</v>
+        <v>16.13633582180884</v>
       </c>
       <c r="F25">
         <v>59.99877615958879</v>
       </c>
       <c r="G25">
-        <v>16.13633582180884</v>
+        <v>23.86488801860238</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>26.06</v>
+      </c>
+      <c r="C26">
         <v>46.62</v>
-      </c>
-      <c r="C26">
-        <v>26.06</v>
       </c>
       <c r="D26">
         <v>2.145002145002145</v>
       </c>
       <c r="E26">
-        <v>26.99791521890202</v>
+        <v>15.09149872596711</v>
       </c>
       <c r="F26">
         <v>57.91058605513088</v>
       </c>
       <c r="G26">
-        <v>15.09149872596711</v>
+        <v>26.99791521890202</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>24.32843385707045</v>
+      </c>
+      <c r="C27">
         <v>39.39432336543335</v>
-      </c>
-      <c r="C27">
-        <v>24.32843385707045</v>
       </c>
       <c r="D27">
         <v>2.538436796397555</v>
       </c>
       <c r="E27">
-        <v>24.06160513892113</v>
+        <v>14.85953099605294</v>
       </c>
       <c r="F27">
-        <v>61.07886386502592</v>
+        <v>61.07886386502593</v>
       </c>
       <c r="G27">
-        <v>14.85953099605294</v>
+        <v>24.06160513892114</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>25.38809831824062</v>
+      </c>
+      <c r="C28">
         <v>33.3764553686934</v>
-      </c>
-      <c r="C28">
-        <v>25.38809831824062</v>
       </c>
       <c r="D28">
         <v>2.996124031007752</v>
       </c>
       <c r="E28">
-        <v>21.02261152984314</v>
+        <v>15.99103687105317</v>
       </c>
       <c r="F28">
         <v>62.98635159910368</v>
       </c>
       <c r="G28">
-        <v>15.99103687105317</v>
+        <v>21.02261152984314</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>34.87323943661972</v>
+      </c>
+      <c r="C29">
         <v>34.92957746478874</v>
-      </c>
-      <c r="C29">
-        <v>34.87323943661972</v>
       </c>
       <c r="D29">
         <v>2.862903225806452</v>
       </c>
       <c r="E29">
-        <v>20.5706702057067</v>
+        <v>20.53749170537492</v>
       </c>
       <c r="F29">
         <v>58.89183808891838</v>
       </c>
       <c r="G29">
-        <v>20.53749170537492</v>
+        <v>20.5706702057067</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>26.47143681477207</v>
+      </c>
+      <c r="C30">
         <v>28.15926139642239</v>
-      </c>
-      <c r="C30">
-        <v>26.47143681477207</v>
       </c>
       <c r="D30">
         <v>3.551229508196721</v>
       </c>
       <c r="E30">
-        <v>18.21065397891595</v>
+        <v>17.11913424759772</v>
       </c>
       <c r="F30">
-        <v>64.67021177348634</v>
+        <v>64.67021177348633</v>
       </c>
       <c r="G30">
-        <v>17.11913424759773</v>
+        <v>18.21065397891594</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>23.8480697384807</v>
+      </c>
+      <c r="C31">
         <v>34.12204234122042</v>
-      </c>
-      <c r="C31">
-        <v>23.8480697384807</v>
       </c>
       <c r="D31">
         <v>2.930656934306569</v>
       </c>
       <c r="E31">
-        <v>21.60031533307055</v>
+        <v>15.09657075285771</v>
       </c>
       <c r="F31">
-        <v>63.30311391407174</v>
+        <v>63.30311391407175</v>
       </c>
       <c r="G31">
-        <v>15.0965707528577</v>
+        <v>21.60031533307056</v>
       </c>
     </row>
   </sheetData>
